--- a/util/Validation/ManualValidation/FeatureEnvyForManual.xlsx
+++ b/util/Validation/ManualValidation/FeatureEnvyForManual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neda/Documents/workspace/DissertationProject/util/Validation/ManualValidation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171C69E9-C6CD-0B4B-AD8F-1F04648A67EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73199D74-43F1-0B47-90B8-3EBA57A474D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39280" yWindow="460" windowWidth="25600" windowHeight="12900" xr2:uid="{572E1FC0-9749-4D45-A225-69C2C6421EF3}"/>
+    <workbookView xWindow="180" yWindow="940" windowWidth="25600" windowHeight="12900" xr2:uid="{572E1FC0-9749-4D45-A225-69C2C6421EF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2746,12 +2746,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2781,13 +2787,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3107,7 +3114,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3176,7 +3185,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -3213,7 +3222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -3250,7 +3259,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -3287,7 +3296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -3324,7 +3333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>841</v>
       </c>
@@ -3361,7 +3370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>843</v>
       </c>
@@ -3398,7 +3407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -3435,7 +3444,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
@@ -3472,7 +3481,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
@@ -3509,7 +3518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
@@ -3546,7 +3555,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
@@ -3583,7 +3592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -3620,7 +3629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
@@ -3657,7 +3666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A18"/>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -3667,7 +3676,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A19"/>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -3677,7 +3686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>24</v>
       </c>
@@ -3714,7 +3723,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
@@ -3751,7 +3760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -3788,7 +3797,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -3825,7 +3834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -3862,7 +3871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>31</v>
       </c>
@@ -3899,7 +3908,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
@@ -3936,7 +3945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -3973,7 +3982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -4010,7 +4019,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>35</v>
       </c>
@@ -4047,7 +4056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>36</v>
       </c>
@@ -4084,7 +4093,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
@@ -4121,7 +4130,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
@@ -4158,7 +4167,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -4195,7 +4204,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -4232,7 +4241,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>42</v>
       </c>
@@ -4269,7 +4278,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>43</v>
       </c>
@@ -4306,7 +4315,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>44</v>
       </c>
@@ -4343,7 +4352,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>45</v>
       </c>
@@ -4380,7 +4389,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>46</v>
       </c>
@@ -4417,7 +4426,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>47</v>
       </c>
@@ -4454,7 +4463,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -4491,7 +4500,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>845</v>
       </c>
@@ -4528,7 +4537,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>54</v>
       </c>
@@ -4565,7 +4574,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>55</v>
       </c>
@@ -4602,7 +4611,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -4639,7 +4648,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>58</v>
       </c>
@@ -4676,7 +4685,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -4713,7 +4722,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>60</v>
       </c>
@@ -4750,7 +4759,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>61</v>
       </c>
@@ -4787,7 +4796,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>62</v>
       </c>
@@ -4824,7 +4833,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>63</v>
       </c>
@@ -4861,7 +4870,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>64</v>
       </c>
@@ -4898,7 +4907,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>65</v>
       </c>
@@ -4935,7 +4944,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>66</v>
       </c>
@@ -4972,7 +4981,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>68</v>
       </c>
@@ -5009,7 +5018,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>69</v>
       </c>
@@ -5046,7 +5055,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>71</v>
       </c>
@@ -5083,7 +5092,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -5120,7 +5129,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>861</v>
       </c>
@@ -5157,7 +5166,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -5194,7 +5203,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>75</v>
       </c>
@@ -5231,7 +5240,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>76</v>
       </c>
@@ -5268,7 +5277,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -5305,7 +5314,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>79</v>
       </c>
@@ -5342,7 +5351,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>846</v>
       </c>
@@ -5379,7 +5388,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>848</v>
       </c>
@@ -5416,7 +5425,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>81</v>
       </c>
@@ -5453,7 +5462,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>83</v>
       </c>
@@ -5490,7 +5499,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>84</v>
       </c>
@@ -5527,7 +5536,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>86</v>
       </c>
@@ -5564,7 +5573,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>87</v>
       </c>
@@ -5601,7 +5610,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>88</v>
       </c>
@@ -5638,7 +5647,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>89</v>
       </c>
@@ -5675,7 +5684,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>90</v>
       </c>
@@ -5712,7 +5721,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>91</v>
       </c>
@@ -5749,7 +5758,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>92</v>
       </c>
@@ -5786,7 +5795,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>93</v>
       </c>
@@ -5823,7 +5832,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>95</v>
       </c>
@@ -5860,7 +5869,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>97</v>
       </c>
@@ -5897,7 +5906,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>98</v>
       </c>
@@ -5934,7 +5943,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>99</v>
       </c>
@@ -5971,7 +5980,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>100</v>
       </c>
@@ -6008,7 +6017,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>101</v>
       </c>
@@ -6045,7 +6054,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>102</v>
       </c>
@@ -6082,7 +6091,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>104</v>
       </c>
@@ -6119,7 +6128,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>106</v>
       </c>
@@ -6156,7 +6165,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>107</v>
       </c>
@@ -6193,7 +6202,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>108</v>
       </c>
@@ -6230,7 +6239,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>110</v>
       </c>
@@ -6267,7 +6276,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>112</v>
       </c>
@@ -6304,7 +6313,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>113</v>
       </c>
@@ -6341,7 +6350,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>114</v>
       </c>
@@ -6378,7 +6387,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>115</v>
       </c>
@@ -6415,7 +6424,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>116</v>
       </c>
@@ -6452,7 +6461,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>117</v>
       </c>
@@ -6489,7 +6498,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>118</v>
       </c>
@@ -6526,7 +6535,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>119</v>
       </c>
@@ -6563,7 +6572,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>121</v>
       </c>
@@ -6600,7 +6609,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>847</v>
       </c>
@@ -6637,7 +6646,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>122</v>
       </c>
@@ -6674,7 +6683,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>123</v>
       </c>
@@ -6711,7 +6720,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>124</v>
       </c>
@@ -6748,7 +6757,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>125</v>
       </c>
@@ -6785,7 +6794,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>126</v>
       </c>
@@ -6822,7 +6831,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>127</v>
       </c>
@@ -6859,7 +6868,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>128</v>
       </c>
@@ -6896,7 +6905,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>129</v>
       </c>
@@ -6933,7 +6942,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>50</v>
       </c>
@@ -6970,7 +6979,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A109"/>
       <c r="E109" t="str">
         <f t="shared" si="4"/>
@@ -6980,7 +6989,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A110"/>
       <c r="E110" t="str">
         <f t="shared" si="4"/>
@@ -6990,7 +6999,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A111"/>
       <c r="E111" t="str">
         <f t="shared" si="4"/>
@@ -7000,7 +7009,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A112"/>
       <c r="E112" t="str">
         <f t="shared" si="4"/>
@@ -7010,7 +7019,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>136</v>
       </c>
@@ -7047,7 +7056,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>137</v>
       </c>
@@ -7084,7 +7093,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>862</v>
       </c>
@@ -7121,7 +7130,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>138</v>
       </c>
@@ -7158,7 +7167,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>139</v>
       </c>
@@ -7195,7 +7204,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A118"/>
       <c r="E118" t="str">
         <f t="shared" si="4"/>
@@ -7205,7 +7214,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>142</v>
       </c>
@@ -7242,7 +7251,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>143</v>
       </c>
@@ -7279,7 +7288,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>144</v>
       </c>
@@ -7316,7 +7325,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A122"/>
       <c r="E122" t="str">
         <f t="shared" si="4"/>
@@ -7326,7 +7335,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A123"/>
       <c r="E123" t="str">
         <f t="shared" si="4"/>
@@ -7336,7 +7345,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>148</v>
       </c>
@@ -7373,7 +7382,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A125"/>
       <c r="E125" t="str">
         <f t="shared" si="4"/>
@@ -7383,7 +7392,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A126"/>
       <c r="E126" t="str">
         <f t="shared" si="4"/>
@@ -7393,7 +7402,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A127"/>
       <c r="E127" t="str">
         <f t="shared" si="4"/>
@@ -7403,7 +7412,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A128"/>
       <c r="E128" t="str">
         <f t="shared" si="4"/>
@@ -7413,7 +7422,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A129"/>
       <c r="E129" t="str">
         <f t="shared" si="4"/>
@@ -7423,7 +7432,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A130"/>
       <c r="E130" t="str">
         <f t="shared" si="4"/>
@@ -7433,7 +7442,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A131"/>
       <c r="E131" t="str">
         <f t="shared" si="4"/>
@@ -7443,7 +7452,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A132"/>
       <c r="E132" t="str">
         <f t="shared" si="4"/>
@@ -7453,7 +7462,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A133"/>
       <c r="E133" t="str">
         <f t="shared" ref="E133:E196" si="6">IF(ISBLANK(A133), "No", "Yes")</f>
@@ -7463,7 +7472,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A134"/>
       <c r="E134" t="str">
         <f t="shared" si="6"/>
@@ -7473,7 +7482,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A135"/>
       <c r="E135" t="str">
         <f t="shared" si="6"/>
@@ -7483,7 +7492,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>162</v>
       </c>
@@ -7520,7 +7529,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>163</v>
       </c>
@@ -7557,7 +7566,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>164</v>
       </c>
@@ -7594,7 +7603,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
         <v>166</v>
       </c>
@@ -7631,7 +7640,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>842</v>
       </c>
@@ -7668,7 +7677,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>844</v>
       </c>
@@ -7705,7 +7714,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A142"/>
       <c r="E142" t="str">
         <f t="shared" si="6"/>
@@ -7715,7 +7724,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>170</v>
       </c>
@@ -7746,7 +7755,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>171</v>
       </c>
@@ -7783,7 +7792,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A145"/>
       <c r="E145" t="str">
         <f t="shared" si="6"/>
@@ -7793,7 +7802,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A146"/>
       <c r="E146" t="str">
         <f t="shared" si="6"/>
@@ -7803,7 +7812,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A147"/>
       <c r="E147" t="str">
         <f t="shared" si="6"/>
@@ -7813,7 +7822,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A148"/>
       <c r="E148" t="str">
         <f t="shared" si="6"/>
@@ -7823,7 +7832,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A149"/>
       <c r="E149" t="str">
         <f t="shared" si="6"/>
@@ -7833,7 +7842,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A150"/>
       <c r="E150" t="str">
         <f t="shared" si="6"/>
@@ -7843,7 +7852,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>178</v>
       </c>
@@ -7880,7 +7889,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A152"/>
       <c r="E152" t="str">
         <f t="shared" si="6"/>
@@ -7890,7 +7899,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A153"/>
       <c r="E153" t="str">
         <f t="shared" si="6"/>
@@ -7900,7 +7909,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A154"/>
       <c r="E154" t="str">
         <f t="shared" si="6"/>
@@ -7910,7 +7919,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A155"/>
       <c r="E155" t="str">
         <f t="shared" si="6"/>
@@ -7920,7 +7929,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A156"/>
       <c r="E156" t="str">
         <f t="shared" si="6"/>
@@ -7930,7 +7939,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A157"/>
       <c r="E157" t="str">
         <f t="shared" si="6"/>
@@ -7940,7 +7949,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A158"/>
       <c r="E158" t="str">
         <f t="shared" si="6"/>
@@ -7950,7 +7959,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
         <v>187</v>
       </c>
@@ -7987,7 +7996,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
         <v>188</v>
       </c>
@@ -8024,7 +8033,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
         <v>189</v>
       </c>
@@ -8061,7 +8070,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
         <v>190</v>
       </c>
@@ -8098,7 +8107,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -8135,7 +8144,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -8172,7 +8181,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
         <v>193</v>
       </c>
@@ -8209,7 +8218,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
         <v>194</v>
       </c>
@@ -8246,7 +8255,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
         <v>195</v>
       </c>
@@ -8283,7 +8292,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
         <v>197</v>
       </c>
@@ -8320,7 +8329,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
         <v>198</v>
       </c>
@@ -8357,7 +8366,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
         <v>202</v>
       </c>
@@ -8394,7 +8403,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
         <v>199</v>
       </c>
@@ -8431,7 +8440,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
         <v>200</v>
       </c>
@@ -8468,7 +8477,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
         <v>201</v>
       </c>
@@ -8505,7 +8514,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A174"/>
       <c r="E174" t="str">
         <f t="shared" si="6"/>
@@ -8515,7 +8524,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A175"/>
       <c r="E175" t="str">
         <f t="shared" si="6"/>
@@ -8525,7 +8534,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A176"/>
       <c r="E176" t="str">
         <f t="shared" si="6"/>
@@ -8535,7 +8544,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
         <v>207</v>
       </c>
@@ -8572,7 +8581,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
         <v>208</v>
       </c>
@@ -8609,7 +8618,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
         <v>210</v>
       </c>
@@ -8646,7 +8655,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
         <v>211</v>
       </c>
@@ -8683,7 +8692,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
         <v>212</v>
       </c>
@@ -8720,7 +8729,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>213</v>
       </c>
@@ -8757,7 +8766,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
         <v>214</v>
       </c>
@@ -8794,7 +8803,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
         <v>215</v>
       </c>
@@ -8831,7 +8840,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
         <v>216</v>
       </c>
@@ -8868,7 +8877,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
         <v>217</v>
       </c>
@@ -8905,7 +8914,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
         <v>218</v>
       </c>
@@ -8942,7 +8951,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A188"/>
       <c r="E188" t="str">
         <f t="shared" si="6"/>
@@ -8952,7 +8961,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>221</v>
       </c>
@@ -8989,7 +8998,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A190"/>
       <c r="E190" t="str">
         <f t="shared" si="6"/>
@@ -8999,7 +9008,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A191"/>
       <c r="E191" t="str">
         <f t="shared" si="6"/>
@@ -9009,7 +9018,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A192"/>
       <c r="E192" t="str">
         <f t="shared" si="6"/>
@@ -9019,7 +9028,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
         <v>226</v>
       </c>
@@ -9056,7 +9065,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>227</v>
       </c>
@@ -9093,7 +9102,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
         <v>228</v>
       </c>
@@ -9130,7 +9139,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
         <v>230</v>
       </c>
@@ -9167,7 +9176,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>232</v>
       </c>
@@ -9204,7 +9213,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A198"/>
       <c r="E198" t="str">
         <f t="shared" si="13"/>
@@ -9214,7 +9223,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
         <v>235</v>
       </c>
@@ -9251,7 +9260,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
         <v>237</v>
       </c>
@@ -9288,7 +9297,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A201"/>
       <c r="E201" t="str">
         <f t="shared" si="13"/>
@@ -9298,7 +9307,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
         <v>241</v>
       </c>
@@ -9335,7 +9344,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>242</v>
       </c>
@@ -9372,7 +9381,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>243</v>
       </c>
@@ -9409,7 +9418,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
         <v>245</v>
       </c>
@@ -9446,7 +9455,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
         <v>247</v>
       </c>
@@ -9483,7 +9492,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A207"/>
       <c r="E207" t="str">
         <f t="shared" si="13"/>
@@ -9493,7 +9502,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A208"/>
       <c r="E208" t="str">
         <f t="shared" si="13"/>
@@ -9503,7 +9512,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A209"/>
       <c r="E209" t="str">
         <f t="shared" si="13"/>
@@ -9513,7 +9522,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A210"/>
       <c r="E210" t="str">
         <f t="shared" si="13"/>
@@ -9523,7 +9532,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>253</v>
       </c>
@@ -9560,7 +9569,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
         <v>254</v>
       </c>
@@ -9597,7 +9606,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
         <v>255</v>
       </c>
@@ -9634,7 +9643,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
         <v>256</v>
       </c>
@@ -9671,7 +9680,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
         <v>257</v>
       </c>
@@ -9708,7 +9717,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
         <v>258</v>
       </c>
@@ -9745,7 +9754,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
         <v>259</v>
       </c>
@@ -9782,7 +9791,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
         <v>260</v>
       </c>
@@ -9819,7 +9828,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A219"/>
       <c r="E219" t="str">
         <f t="shared" si="13"/>
@@ -9829,7 +9838,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A220"/>
       <c r="E220" t="str">
         <f t="shared" si="13"/>
@@ -9839,7 +9848,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
         <v>264</v>
       </c>
@@ -9876,7 +9885,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
         <v>265</v>
       </c>
@@ -9913,7 +9922,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
         <v>266</v>
       </c>
@@ -9950,7 +9959,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
         <v>80</v>
       </c>
@@ -9987,7 +9996,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A225"/>
       <c r="E225" t="str">
         <f t="shared" si="13"/>
@@ -9997,7 +10006,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A226"/>
       <c r="E226" t="str">
         <f t="shared" si="13"/>
@@ -10007,7 +10016,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A227" s="3" t="s">
         <v>270</v>
       </c>
@@ -10044,7 +10053,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A228"/>
       <c r="E228" t="str">
         <f t="shared" si="13"/>
@@ -10054,7 +10063,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A229"/>
       <c r="E229" t="str">
         <f t="shared" si="13"/>
@@ -10064,7 +10073,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
         <v>274</v>
       </c>
@@ -10101,7 +10110,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
         <v>275</v>
       </c>
@@ -10138,7 +10147,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
         <v>276</v>
       </c>
@@ -10175,7 +10184,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
         <v>278</v>
       </c>
@@ -10212,7 +10221,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
         <v>279</v>
       </c>
@@ -10249,7 +10258,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
         <v>280</v>
       </c>
@@ -10286,7 +10295,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
         <v>281</v>
       </c>
@@ -10323,7 +10332,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
         <v>282</v>
       </c>
@@ -10360,7 +10369,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
         <v>283</v>
       </c>
@@ -10397,7 +10406,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>149</v>
       </c>
@@ -10434,7 +10443,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A240"/>
       <c r="E240" t="str">
         <f t="shared" si="13"/>
@@ -10444,7 +10453,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A241"/>
       <c r="E241" t="str">
         <f t="shared" si="13"/>
@@ -10454,7 +10463,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A242"/>
       <c r="E242" t="str">
         <f t="shared" si="13"/>
@@ -10464,7 +10473,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
         <v>288</v>
       </c>
@@ -10501,7 +10510,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>289</v>
       </c>
@@ -10538,7 +10547,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>290</v>
       </c>
@@ -10575,7 +10584,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>291</v>
       </c>
@@ -10612,7 +10621,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>863</v>
       </c>
@@ -10648,7 +10657,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>292</v>
       </c>
@@ -10685,7 +10694,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A249"/>
       <c r="E249" t="str">
         <f t="shared" si="13"/>
@@ -10695,7 +10704,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>295</v>
       </c>
@@ -10732,7 +10741,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A251"/>
       <c r="E251" t="str">
         <f t="shared" si="13"/>
@@ -10742,7 +10751,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
         <v>298</v>
       </c>
@@ -10779,7 +10788,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
         <v>299</v>
       </c>
@@ -10816,7 +10825,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
         <v>300</v>
       </c>
@@ -10853,7 +10862,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>301</v>
       </c>
@@ -10890,7 +10899,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
         <v>302</v>
       </c>
@@ -10927,7 +10936,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A257"/>
       <c r="E257" t="str">
         <f t="shared" si="13"/>
@@ -10937,7 +10946,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A258"/>
       <c r="E258" t="str">
         <f t="shared" si="13"/>
@@ -10947,7 +10956,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
         <v>306</v>
       </c>
@@ -10984,7 +10993,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>308</v>
       </c>
@@ -11021,7 +11030,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A261" s="3" t="s">
         <v>309</v>
       </c>
@@ -11058,7 +11067,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
         <v>310</v>
       </c>
@@ -11095,7 +11104,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
         <v>314</v>
       </c>
@@ -11132,7 +11141,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
         <v>315</v>
       </c>
@@ -11169,7 +11178,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
         <v>317</v>
       </c>
@@ -11206,7 +11215,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
         <v>318</v>
       </c>
@@ -11243,7 +11252,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A267" s="3" t="s">
         <v>319</v>
       </c>
@@ -11280,7 +11289,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A268" s="3" t="s">
         <v>320</v>
       </c>
@@ -11317,7 +11326,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A269" s="3" t="s">
         <v>322</v>
       </c>
@@ -11354,7 +11363,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A270" s="3" t="s">
         <v>324</v>
       </c>
@@ -11391,7 +11400,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A271"/>
       <c r="E271" t="str">
         <f t="shared" si="21"/>
@@ -11401,7 +11410,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A272" s="3" t="s">
         <v>327</v>
       </c>
@@ -11438,7 +11447,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A273" s="3" t="s">
         <v>328</v>
       </c>
@@ -11475,7 +11484,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A274" s="3" t="s">
         <v>329</v>
       </c>
@@ -11512,7 +11521,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A275" s="3" t="s">
         <v>330</v>
       </c>
@@ -11549,7 +11558,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A276" s="3" t="s">
         <v>331</v>
       </c>
@@ -11586,7 +11595,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A277" s="3" t="s">
         <v>332</v>
       </c>
@@ -11623,7 +11632,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A278" s="3" t="s">
         <v>333</v>
       </c>
@@ -11660,7 +11669,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A279" s="3" t="s">
         <v>334</v>
       </c>
@@ -11697,7 +11706,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A280" s="3" t="s">
         <v>335</v>
       </c>
@@ -11734,7 +11743,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A281" s="3" t="s">
         <v>336</v>
       </c>
@@ -11771,7 +11780,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
         <v>337</v>
       </c>
@@ -11808,7 +11817,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A283" s="3" t="s">
         <v>338</v>
       </c>
@@ -11845,7 +11854,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A284" s="3" t="s">
         <v>339</v>
       </c>
@@ -11882,7 +11891,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A285" s="3" t="s">
         <v>340</v>
       </c>
@@ -11919,7 +11928,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A286" s="3" t="s">
         <v>341</v>
       </c>
@@ -11956,7 +11965,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A287" s="3" t="s">
         <v>342</v>
       </c>
@@ -11993,7 +12002,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A288" s="3" t="s">
         <v>343</v>
       </c>
@@ -12030,7 +12039,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A289" s="3" t="s">
         <v>344</v>
       </c>
@@ -12067,7 +12076,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A290" s="3" t="s">
         <v>345</v>
       </c>
@@ -12104,7 +12113,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A291" s="3" t="s">
         <v>346</v>
       </c>
@@ -12141,7 +12150,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A292" s="3" t="s">
         <v>347</v>
       </c>
@@ -12178,7 +12187,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A293" s="3" t="s">
         <v>348</v>
       </c>
@@ -12215,7 +12224,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A294" s="3" t="s">
         <v>349</v>
       </c>
@@ -12252,7 +12261,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A295" s="3" t="s">
         <v>350</v>
       </c>
@@ -12289,7 +12298,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A296" s="3" t="s">
         <v>351</v>
       </c>
@@ -12326,7 +12335,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A297" s="3" t="s">
         <v>352</v>
       </c>
@@ -12363,7 +12372,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A298" s="3" t="s">
         <v>353</v>
       </c>
@@ -12400,7 +12409,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A299" s="3" t="s">
         <v>354</v>
       </c>
@@ -12437,7 +12446,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A300" s="3" t="s">
         <v>355</v>
       </c>
@@ -12474,7 +12483,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A301" s="3" t="s">
         <v>356</v>
       </c>
@@ -12511,7 +12520,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
         <v>357</v>
       </c>
@@ -12548,7 +12557,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A303" s="3" t="s">
         <v>358</v>
       </c>
@@ -12585,7 +12594,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A304" s="3" t="s">
         <v>359</v>
       </c>
@@ -12622,7 +12631,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A305" s="3" t="s">
         <v>361</v>
       </c>
@@ -12659,7 +12668,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
         <v>362</v>
       </c>
@@ -12696,7 +12705,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A307" s="3" t="s">
         <v>363</v>
       </c>
@@ -12733,7 +12742,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A308" s="3" t="s">
         <v>360</v>
       </c>
@@ -12770,7 +12779,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A309" s="3" t="s">
         <v>364</v>
       </c>
@@ -12807,7 +12816,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
         <v>365</v>
       </c>
@@ -12844,7 +12853,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A311" s="3" t="s">
         <v>366</v>
       </c>
@@ -12881,7 +12890,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
         <v>367</v>
       </c>
@@ -12918,7 +12927,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A313" s="3" t="s">
         <v>368</v>
       </c>
@@ -12955,7 +12964,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
         <v>369</v>
       </c>
@@ -12992,7 +13001,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
         <v>378</v>
       </c>
@@ -13029,8 +13038,8 @@
         <v>326</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A316" t="s">
+    <row r="316" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A316" s="4" t="s">
         <v>379</v>
       </c>
       <c r="B316">
@@ -13066,7 +13075,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="3" t="s">
         <v>380</v>
       </c>
@@ -13103,7 +13112,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="3" t="s">
         <v>370</v>
       </c>
@@ -13140,7 +13149,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="3" t="s">
         <v>381</v>
       </c>
@@ -13177,7 +13186,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="3" t="s">
         <v>382</v>
       </c>
@@ -13214,7 +13223,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>383</v>
       </c>
@@ -13251,7 +13260,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="3" t="s">
         <v>371</v>
       </c>
@@ -13288,7 +13297,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="3" t="s">
         <v>384</v>
       </c>
@@ -13325,7 +13334,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="3" t="s">
         <v>385</v>
       </c>
@@ -13362,7 +13371,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="3" t="s">
         <v>386</v>
       </c>
@@ -13399,7 +13408,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="3" t="s">
         <v>372</v>
       </c>
@@ -13436,7 +13445,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>373</v>
       </c>
@@ -13473,7 +13482,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="3" t="s">
         <v>374</v>
       </c>
@@ -13510,7 +13519,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="3" t="s">
         <v>387</v>
       </c>
@@ -13547,7 +13556,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="3" t="s">
         <v>375</v>
       </c>
@@ -13584,7 +13593,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="3" t="s">
         <v>388</v>
       </c>
@@ -13621,7 +13630,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="3" t="s">
         <v>389</v>
       </c>
@@ -13658,7 +13667,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="3" t="s">
         <v>390</v>
       </c>
@@ -13695,7 +13704,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="3" t="s">
         <v>391</v>
       </c>
@@ -13732,7 +13741,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="3" t="s">
         <v>392</v>
       </c>
@@ -13769,7 +13778,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="3" t="s">
         <v>393</v>
       </c>
@@ -13806,7 +13815,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="3" t="s">
         <v>394</v>
       </c>
@@ -13843,7 +13852,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
         <v>395</v>
       </c>
@@ -13880,7 +13889,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="3" t="s">
         <v>376</v>
       </c>
@@ -13917,7 +13926,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="3" t="s">
         <v>396</v>
       </c>
@@ -13954,7 +13963,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="3" t="s">
         <v>397</v>
       </c>
@@ -13991,7 +14000,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="3" t="s">
         <v>398</v>
       </c>
@@ -14028,7 +14037,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="3" t="s">
         <v>399</v>
       </c>
@@ -14065,7 +14074,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="3" t="s">
         <v>400</v>
       </c>
@@ -14102,7 +14111,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="3" t="s">
         <v>401</v>
       </c>
@@ -14139,7 +14148,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
         <v>402</v>
       </c>
@@ -14176,7 +14185,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>377</v>
       </c>
@@ -14213,7 +14222,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="3" t="s">
         <v>403</v>
       </c>
@@ -14250,7 +14259,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="3" t="s">
         <v>404</v>
       </c>
@@ -14287,7 +14296,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
         <v>405</v>
       </c>
@@ -14324,7 +14333,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="3" t="s">
         <v>406</v>
       </c>
@@ -14361,7 +14370,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="3" t="s">
         <v>407</v>
       </c>
@@ -14398,7 +14407,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="3" t="s">
         <v>408</v>
       </c>
@@ -14435,7 +14444,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="3" t="s">
         <v>409</v>
       </c>
@@ -14472,7 +14481,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="3" t="s">
         <v>410</v>
       </c>
@@ -14509,7 +14518,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="3" t="s">
         <v>411</v>
       </c>
@@ -14546,7 +14555,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" s="3" t="s">
         <v>412</v>
       </c>
@@ -14583,7 +14592,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="3" t="s">
         <v>413</v>
       </c>
@@ -14620,7 +14629,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="3" t="s">
         <v>414</v>
       </c>
@@ -14687,7 +14696,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="3" t="s">
         <v>419</v>
       </c>
@@ -14724,7 +14733,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>48</v>
       </c>
@@ -14761,7 +14770,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>49</v>
       </c>
@@ -14798,7 +14807,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="3" t="s">
         <v>423</v>
       </c>
@@ -14835,7 +14844,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="3" t="s">
         <v>425</v>
       </c>
@@ -14872,7 +14881,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>427</v>
       </c>
@@ -14909,7 +14918,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>429</v>
       </c>
@@ -14946,7 +14955,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>431</v>
       </c>
@@ -14983,7 +14992,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="3" t="s">
         <v>432</v>
       </c>
@@ -15020,7 +15029,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>434</v>
       </c>
@@ -15057,7 +15066,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="3" t="s">
         <v>435</v>
       </c>
@@ -15094,7 +15103,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="3" t="s">
         <v>437</v>
       </c>
@@ -15131,7 +15140,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="3" t="s">
         <v>439</v>
       </c>
@@ -15168,7 +15177,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="3" t="s">
         <v>441</v>
       </c>
@@ -15205,7 +15214,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="3" t="s">
         <v>443</v>
       </c>
@@ -15242,7 +15251,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="3" t="s">
         <v>445</v>
       </c>
@@ -15279,7 +15288,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>447</v>
       </c>
@@ -15316,7 +15325,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="3" t="s">
         <v>449</v>
       </c>
@@ -15353,7 +15362,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="3" t="s">
         <v>451</v>
       </c>
@@ -15391,7 +15400,7 @@
       </c>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A382" t="s">
+      <c r="A382" s="4" t="s">
         <v>452</v>
       </c>
       <c r="B382">
@@ -15427,7 +15436,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>455</v>
       </c>
@@ -15464,7 +15473,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>457</v>
       </c>
@@ -15501,7 +15510,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="3" t="s">
         <v>458</v>
       </c>
@@ -15538,7 +15547,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="3" t="s">
         <v>460</v>
       </c>
@@ -15575,7 +15584,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="3" t="s">
         <v>462</v>
       </c>
@@ -15612,7 +15621,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="3" t="s">
         <v>464</v>
       </c>
@@ -15649,7 +15658,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>466</v>
       </c>
@@ -15687,7 +15696,7 @@
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A390" t="s">
+      <c r="A390" s="4" t="s">
         <v>467</v>
       </c>
       <c r="B390">
@@ -15723,7 +15732,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>469</v>
       </c>
@@ -15760,7 +15769,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>470</v>
       </c>
@@ -15797,7 +15806,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="3" t="s">
         <v>473</v>
       </c>
@@ -15834,7 +15843,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>474</v>
       </c>
@@ -15871,7 +15880,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="3" t="s">
         <v>475</v>
       </c>
@@ -15908,7 +15917,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="3" t="s">
         <v>476</v>
       </c>
@@ -15945,7 +15954,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>477</v>
       </c>
@@ -15982,7 +15991,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="3" t="s">
         <v>478</v>
       </c>
@@ -16019,7 +16028,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="3" t="s">
         <v>479</v>
       </c>
@@ -16056,7 +16065,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="3" t="s">
         <v>481</v>
       </c>
@@ -16093,7 +16102,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>483</v>
       </c>
@@ -16130,7 +16139,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="3" t="s">
         <v>485</v>
       </c>
@@ -16167,7 +16176,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="3" t="s">
         <v>486</v>
       </c>
@@ -16204,7 +16213,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="3" t="s">
         <v>487</v>
       </c>
@@ -16241,7 +16250,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="3" t="s">
         <v>489</v>
       </c>
@@ -16278,7 +16287,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>491</v>
       </c>
@@ -16315,7 +16324,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="3" t="s">
         <v>493</v>
       </c>
@@ -16352,7 +16361,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>495</v>
       </c>
@@ -16389,7 +16398,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>496</v>
       </c>
@@ -16426,7 +16435,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>498</v>
       </c>
@@ -16463,7 +16472,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="3" t="s">
         <v>500</v>
       </c>
@@ -16560,7 +16569,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="3" t="s">
         <v>508</v>
       </c>
@@ -16597,7 +16606,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="3" t="s">
         <v>509</v>
       </c>
@@ -16764,7 +16773,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="3" t="s">
         <v>523</v>
       </c>
@@ -16851,7 +16860,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" s="3" t="s">
         <v>530</v>
       </c>
@@ -16888,7 +16897,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="3" t="s">
         <v>531</v>
       </c>
@@ -16926,7 +16935,7 @@
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A441" t="s">
+      <c r="A441" s="4" t="s">
         <v>532</v>
       </c>
       <c r="B441">
@@ -16962,7 +16971,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" s="3" t="s">
         <v>534</v>
       </c>
@@ -17019,7 +17028,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="3" t="s">
         <v>538</v>
       </c>
@@ -17066,7 +17075,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="3" t="s">
         <v>541</v>
       </c>
@@ -17113,7 +17122,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" s="3" t="s">
         <v>544</v>
       </c>
@@ -17150,7 +17159,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="3" t="s">
         <v>545</v>
       </c>
@@ -17187,7 +17196,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" s="3" t="s">
         <v>546</v>
       </c>
@@ -17224,7 +17233,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="3" t="s">
         <v>547</v>
       </c>
@@ -17261,7 +17270,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="3" t="s">
         <v>548</v>
       </c>
@@ -17298,7 +17307,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="3" t="s">
         <v>549</v>
       </c>
@@ -17335,7 +17344,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" s="3" t="s">
         <v>550</v>
       </c>
@@ -17372,7 +17381,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="3" t="s">
         <v>551</v>
       </c>
@@ -17409,7 +17418,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="3" t="s">
         <v>552</v>
       </c>
@@ -17446,7 +17455,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="3" t="s">
         <v>554</v>
       </c>
@@ -17493,7 +17502,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" s="3" t="s">
         <v>557</v>
       </c>
@@ -17530,7 +17539,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>558</v>
       </c>
@@ -17567,7 +17576,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" s="3" t="s">
         <v>559</v>
       </c>
@@ -17604,7 +17613,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="3" t="s">
         <v>849</v>
       </c>
@@ -17641,7 +17650,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="3" t="s">
         <v>561</v>
       </c>
@@ -17718,7 +17727,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" s="3" t="s">
         <v>567</v>
       </c>
@@ -17785,7 +17794,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="3" t="s">
         <v>572</v>
       </c>
@@ -17822,7 +17831,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="3" t="s">
         <v>574</v>
       </c>
@@ -17869,7 +17878,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="3" t="s">
         <v>577</v>
       </c>
@@ -17906,7 +17915,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="3" t="s">
         <v>579</v>
       </c>
@@ -17943,7 +17952,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="3" t="s">
         <v>581</v>
       </c>
@@ -17980,7 +17989,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="3" t="s">
         <v>582</v>
       </c>
@@ -18017,7 +18026,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="3" t="s">
         <v>583</v>
       </c>
@@ -18054,7 +18063,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="3" t="s">
         <v>584</v>
       </c>
@@ -18091,7 +18100,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="3" t="s">
         <v>586</v>
       </c>
@@ -18128,7 +18137,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="3" t="s">
         <v>587</v>
       </c>
@@ -18165,7 +18174,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="3" t="s">
         <v>589</v>
       </c>
@@ -18202,7 +18211,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" s="3" t="s">
         <v>590</v>
       </c>
@@ -18239,7 +18248,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="3" t="s">
         <v>591</v>
       </c>
@@ -18276,7 +18285,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="3" t="s">
         <v>592</v>
       </c>
@@ -18313,7 +18322,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" s="3" t="s">
         <v>593</v>
       </c>
@@ -18370,7 +18379,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="3" t="s">
         <v>597</v>
       </c>
@@ -18407,7 +18416,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="3" t="s">
         <v>598</v>
       </c>
@@ -18444,7 +18453,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="3" t="s">
         <v>599</v>
       </c>
@@ -18481,7 +18490,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="3" t="s">
         <v>600</v>
       </c>
@@ -18518,7 +18527,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="3" t="s">
         <v>601</v>
       </c>
@@ -18555,7 +18564,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="3" t="s">
         <v>602</v>
       </c>
@@ -18592,7 +18601,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="3" t="s">
         <v>603</v>
       </c>
@@ -18629,7 +18638,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" s="3" t="s">
         <v>604</v>
       </c>
@@ -18666,7 +18675,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" s="3" t="s">
         <v>605</v>
       </c>
@@ -18703,7 +18712,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" s="3" t="s">
         <v>606</v>
       </c>
@@ -18740,7 +18749,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>607</v>
       </c>
@@ -18777,7 +18786,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" s="3" t="s">
         <v>608</v>
       </c>
@@ -18814,7 +18823,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" s="3" t="s">
         <v>609</v>
       </c>
@@ -18851,7 +18860,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" s="3" t="s">
         <v>610</v>
       </c>
@@ -18889,7 +18898,7 @@
       </c>
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A505" t="s">
+      <c r="A505" s="4" t="s">
         <v>611</v>
       </c>
       <c r="B505">
@@ -18925,7 +18934,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>612</v>
       </c>
@@ -18963,7 +18972,7 @@
       </c>
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A507" t="s">
+      <c r="A507" s="4" t="s">
         <v>613</v>
       </c>
       <c r="B507">
@@ -18999,7 +19008,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" s="3" t="s">
         <v>614</v>
       </c>
@@ -19036,7 +19045,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" s="3" t="s">
         <v>615</v>
       </c>
@@ -19073,7 +19082,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="3" t="s">
         <v>616</v>
       </c>
@@ -19110,7 +19119,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" s="3" t="s">
         <v>618</v>
       </c>
@@ -19147,7 +19156,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" s="3" t="s">
         <v>619</v>
       </c>
@@ -19184,7 +19193,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" s="3" t="s">
         <v>620</v>
       </c>
@@ -19221,7 +19230,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" s="3" t="s">
         <v>621</v>
       </c>
@@ -19258,7 +19267,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" s="3" t="s">
         <v>622</v>
       </c>
@@ -19295,7 +19304,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" s="3" t="s">
         <v>623</v>
       </c>
@@ -19332,7 +19341,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" s="3" t="s">
         <v>624</v>
       </c>
@@ -19370,7 +19379,7 @@
       </c>
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A518" t="s">
+      <c r="A518" s="4" t="s">
         <v>626</v>
       </c>
       <c r="B518">
@@ -19426,7 +19435,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" s="3" t="s">
         <v>630</v>
       </c>
@@ -19473,7 +19482,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>633</v>
       </c>
@@ -19531,7 +19540,7 @@
       </c>
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A526" t="s">
+      <c r="A526" s="4" t="s">
         <v>637</v>
       </c>
       <c r="B526">
@@ -19560,14 +19569,14 @@
         <v>143</v>
       </c>
       <c r="J526" t="str">
-        <f>IF(AND(AND((F526&gt;4), (F526&lt;=I526)),AND((G526&gt;3), (H526&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J526:J533" si="39">IF(AND(AND((F526&gt;4), (F526&lt;=I526)),AND((G526&gt;3), (H526&lt;3))), "TRUE", "FALSE")</f>
         <v>TRUE</v>
       </c>
       <c r="K526" s="1" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" s="3" t="s">
         <v>639</v>
       </c>
@@ -19597,14 +19606,14 @@
         <v>17</v>
       </c>
       <c r="J527" t="str">
-        <f>IF(AND(AND((F527&gt;4), (F527&lt;=I527)),AND((G527&gt;3), (H527&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="39"/>
         <v>FALSE</v>
       </c>
       <c r="K527" s="1" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" s="3" t="s">
         <v>641</v>
       </c>
@@ -19634,14 +19643,14 @@
         <v>14</v>
       </c>
       <c r="J528" t="str">
-        <f>IF(AND(AND((F528&gt;4), (F528&lt;=I528)),AND((G528&gt;3), (H528&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="39"/>
         <v>FALSE</v>
       </c>
       <c r="K528" s="1" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" s="3" t="s">
         <v>643</v>
       </c>
@@ -19671,14 +19680,14 @@
         <v>14</v>
       </c>
       <c r="J529" t="str">
-        <f>IF(AND(AND((F529&gt;4), (F529&lt;=I529)),AND((G529&gt;3), (H529&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="39"/>
         <v>FALSE</v>
       </c>
       <c r="K529" s="1" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" s="3" t="s">
         <v>645</v>
       </c>
@@ -19708,14 +19717,14 @@
         <v>14</v>
       </c>
       <c r="J530" t="str">
-        <f>IF(AND(AND((F530&gt;4), (F530&lt;=I530)),AND((G530&gt;3), (H530&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="39"/>
         <v>FALSE</v>
       </c>
       <c r="K530" s="1" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" s="3" t="s">
         <v>647</v>
       </c>
@@ -19745,14 +19754,14 @@
         <v>14</v>
       </c>
       <c r="J531" t="str">
-        <f>IF(AND(AND((F531&gt;4), (F531&lt;=I531)),AND((G531&gt;3), (H531&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="39"/>
         <v>FALSE</v>
       </c>
       <c r="K531" s="1" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" s="3" t="s">
         <v>649</v>
       </c>
@@ -19782,14 +19791,14 @@
         <v>15</v>
       </c>
       <c r="J532" t="str">
-        <f>IF(AND(AND((F532&gt;4), (F532&lt;=I532)),AND((G532&gt;3), (H532&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="39"/>
         <v>FALSE</v>
       </c>
       <c r="K532" s="1" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" s="3" t="s">
         <v>850</v>
       </c>
@@ -19819,7 +19828,7 @@
         <v>0</v>
       </c>
       <c r="J533" t="str">
-        <f>IF(AND(AND((F533&gt;4), (F533&lt;=I533)),AND((G533&gt;3), (H533&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="39"/>
         <v>FALSE</v>
       </c>
       <c r="K533" s="1" t="s">
@@ -19926,7 +19935,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" s="3" t="s">
         <v>665</v>
       </c>
@@ -20003,7 +20012,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" s="3" t="s">
         <v>671</v>
       </c>
@@ -20033,14 +20042,14 @@
         <v>28</v>
       </c>
       <c r="J549" t="str">
-        <f>IF(AND(AND((F549&gt;4), (F549&lt;=I549)),AND((G549&gt;3), (H549&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J549:J566" si="40">IF(AND(AND((F549&gt;4), (F549&lt;=I549)),AND((G549&gt;3), (H549&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K549" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" s="3" t="s">
         <v>672</v>
       </c>
@@ -20070,14 +20079,14 @@
         <v>6</v>
       </c>
       <c r="J550" t="str">
-        <f>IF(AND(AND((F550&gt;4), (F550&lt;=I550)),AND((G550&gt;3), (H550&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K550" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" s="3" t="s">
         <v>673</v>
       </c>
@@ -20107,14 +20116,14 @@
         <v>1</v>
       </c>
       <c r="J551" t="str">
-        <f>IF(AND(AND((F551&gt;4), (F551&lt;=I551)),AND((G551&gt;3), (H551&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K551" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>674</v>
       </c>
@@ -20144,14 +20153,14 @@
         <v>19</v>
       </c>
       <c r="J552" t="str">
-        <f>IF(AND(AND((F552&gt;4), (F552&lt;=I552)),AND((G552&gt;3), (H552&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K552" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" s="3" t="s">
         <v>675</v>
       </c>
@@ -20181,14 +20190,14 @@
         <v>0</v>
       </c>
       <c r="J553" t="str">
-        <f>IF(AND(AND((F553&gt;4), (F553&lt;=I553)),AND((G553&gt;3), (H553&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K553" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" s="3" t="s">
         <v>676</v>
       </c>
@@ -20218,14 +20227,14 @@
         <v>4</v>
       </c>
       <c r="J554" t="str">
-        <f>IF(AND(AND((F554&gt;4), (F554&lt;=I554)),AND((G554&gt;3), (H554&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K554" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" s="3" t="s">
         <v>677</v>
       </c>
@@ -20255,14 +20264,14 @@
         <v>7</v>
       </c>
       <c r="J555" t="str">
-        <f>IF(AND(AND((F555&gt;4), (F555&lt;=I555)),AND((G555&gt;3), (H555&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K555" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" s="3" t="s">
         <v>678</v>
       </c>
@@ -20292,14 +20301,14 @@
         <v>4</v>
       </c>
       <c r="J556" t="str">
-        <f>IF(AND(AND((F556&gt;4), (F556&lt;=I556)),AND((G556&gt;3), (H556&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K556" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" s="3" t="s">
         <v>680</v>
       </c>
@@ -20329,14 +20338,14 @@
         <v>65</v>
       </c>
       <c r="J557" t="str">
-        <f>IF(AND(AND((F557&gt;4), (F557&lt;=I557)),AND((G557&gt;3), (H557&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K557" s="1" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" s="3" t="s">
         <v>682</v>
       </c>
@@ -20366,14 +20375,14 @@
         <v>4</v>
       </c>
       <c r="J558" t="str">
-        <f>IF(AND(AND((F558&gt;4), (F558&lt;=I558)),AND((G558&gt;3), (H558&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K558" s="1" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" s="3" t="s">
         <v>683</v>
       </c>
@@ -20403,14 +20412,14 @@
         <v>41</v>
       </c>
       <c r="J559" t="str">
-        <f>IF(AND(AND((F559&gt;4), (F559&lt;=I559)),AND((G559&gt;3), (H559&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K559" s="1" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" s="3" t="s">
         <v>685</v>
       </c>
@@ -20440,14 +20449,14 @@
         <v>0</v>
       </c>
       <c r="J560" t="str">
-        <f>IF(AND(AND((F560&gt;4), (F560&lt;=I560)),AND((G560&gt;3), (H560&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K560" s="1" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" s="3" t="s">
         <v>686</v>
       </c>
@@ -20477,14 +20486,14 @@
         <v>0</v>
       </c>
       <c r="J561" t="str">
-        <f>IF(AND(AND((F561&gt;4), (F561&lt;=I561)),AND((G561&gt;3), (H561&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K561" s="1" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" s="3" t="s">
         <v>687</v>
       </c>
@@ -20514,14 +20523,14 @@
         <v>0</v>
       </c>
       <c r="J562" t="str">
-        <f>IF(AND(AND((F562&gt;4), (F562&lt;=I562)),AND((G562&gt;3), (H562&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K562" s="1" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" s="3" t="s">
         <v>688</v>
       </c>
@@ -20551,14 +20560,14 @@
         <v>11</v>
       </c>
       <c r="J563" t="str">
-        <f>IF(AND(AND((F563&gt;4), (F563&lt;=I563)),AND((G563&gt;3), (H563&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K563" s="1" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" s="3" t="s">
         <v>689</v>
       </c>
@@ -20588,14 +20597,14 @@
         <v>40</v>
       </c>
       <c r="J564" t="str">
-        <f>IF(AND(AND((F564&gt;4), (F564&lt;=I564)),AND((G564&gt;3), (H564&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K564" s="1" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" s="3" t="s">
         <v>691</v>
       </c>
@@ -20625,14 +20634,14 @@
         <v>2</v>
       </c>
       <c r="J565" t="str">
-        <f>IF(AND(AND((F565&gt;4), (F565&lt;=I565)),AND((G565&gt;3), (H565&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K565" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" s="3" t="s">
         <v>692</v>
       </c>
@@ -20662,14 +20671,14 @@
         <v>0</v>
       </c>
       <c r="J566" t="str">
-        <f>IF(AND(AND((F566&gt;4), (F566&lt;=I566)),AND((G566&gt;3), (H566&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" si="40"/>
         <v>FALSE</v>
       </c>
       <c r="K566" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" s="3" t="s">
         <v>693</v>
       </c>
@@ -20699,14 +20708,14 @@
         <v>0</v>
       </c>
       <c r="J567" t="str">
-        <f t="shared" ref="J567:J601" si="39">IF(AND(AND((F567&gt;4), (F567&lt;=I567)),AND((G567&gt;3), (H567&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J567:J601" si="41">IF(AND(AND((F567&gt;4), (F567&lt;=I567)),AND((G567&gt;3), (H567&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K567" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" s="3" t="s">
         <v>694</v>
       </c>
@@ -20736,14 +20745,14 @@
         <v>0</v>
       </c>
       <c r="J568" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K568" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" s="3" t="s">
         <v>695</v>
       </c>
@@ -20773,14 +20782,14 @@
         <v>0</v>
       </c>
       <c r="J569" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K569" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" s="3" t="s">
         <v>696</v>
       </c>
@@ -20810,14 +20819,14 @@
         <v>0</v>
       </c>
       <c r="J570" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K570" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" s="3" t="s">
         <v>697</v>
       </c>
@@ -20847,14 +20856,14 @@
         <v>0</v>
       </c>
       <c r="J571" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K571" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" s="3" t="s">
         <v>698</v>
       </c>
@@ -20884,14 +20893,14 @@
         <v>0</v>
       </c>
       <c r="J572" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K572" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" s="3" t="s">
         <v>699</v>
       </c>
@@ -20921,7 +20930,7 @@
         <v>0</v>
       </c>
       <c r="J573" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K573" s="1" t="s">
@@ -20938,7 +20947,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" s="3" t="s">
         <v>703</v>
       </c>
@@ -20968,14 +20977,14 @@
         <v>0</v>
       </c>
       <c r="J575" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K575" s="1" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>705</v>
       </c>
@@ -21005,14 +21014,14 @@
         <v>0</v>
       </c>
       <c r="J576" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K576" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" s="3" t="s">
         <v>706</v>
       </c>
@@ -21042,14 +21051,14 @@
         <v>0</v>
       </c>
       <c r="J577" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K577" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>707</v>
       </c>
@@ -21063,7 +21072,7 @@
         <v>0</v>
       </c>
       <c r="E578" t="str">
-        <f t="shared" ref="E578:E641" si="40">IF(ISBLANK(A578), "No", "Yes")</f>
+        <f t="shared" ref="E578:E641" si="42">IF(ISBLANK(A578), "No", "Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F578">
@@ -21079,14 +21088,14 @@
         <v>0</v>
       </c>
       <c r="J578" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K578" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" s="3" t="s">
         <v>708</v>
       </c>
@@ -21100,7 +21109,7 @@
         <v>0</v>
       </c>
       <c r="E579" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F579">
@@ -21116,14 +21125,14 @@
         <v>0</v>
       </c>
       <c r="J579" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K579" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>709</v>
       </c>
@@ -21137,7 +21146,7 @@
         <v>0</v>
       </c>
       <c r="E580" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F580">
@@ -21153,14 +21162,14 @@
         <v>0</v>
       </c>
       <c r="J580" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K580" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>710</v>
       </c>
@@ -21174,7 +21183,7 @@
         <v>0</v>
       </c>
       <c r="E581" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F581">
@@ -21190,14 +21199,14 @@
         <v>0</v>
       </c>
       <c r="J581" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K581" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" s="3" t="s">
         <v>711</v>
       </c>
@@ -21211,7 +21220,7 @@
         <v>0</v>
       </c>
       <c r="E582" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F582">
@@ -21227,14 +21236,14 @@
         <v>0</v>
       </c>
       <c r="J582" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K582" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>712</v>
       </c>
@@ -21248,7 +21257,7 @@
         <v>0</v>
       </c>
       <c r="E583" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F583">
@@ -21264,14 +21273,14 @@
         <v>0</v>
       </c>
       <c r="J583" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K583" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>713</v>
       </c>
@@ -21285,7 +21294,7 @@
         <v>0</v>
       </c>
       <c r="E584" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F584">
@@ -21301,14 +21310,14 @@
         <v>0</v>
       </c>
       <c r="J584" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K584" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" s="3" t="s">
         <v>714</v>
       </c>
@@ -21322,7 +21331,7 @@
         <v>0</v>
       </c>
       <c r="E585" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F585">
@@ -21338,14 +21347,14 @@
         <v>0</v>
       </c>
       <c r="J585" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K585" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" s="3" t="s">
         <v>715</v>
       </c>
@@ -21359,7 +21368,7 @@
         <v>0</v>
       </c>
       <c r="E586" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F586">
@@ -21375,14 +21384,14 @@
         <v>0</v>
       </c>
       <c r="J586" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K586" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" s="3" t="s">
         <v>716</v>
       </c>
@@ -21396,7 +21405,7 @@
         <v>0</v>
       </c>
       <c r="E587" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F587">
@@ -21412,14 +21421,14 @@
         <v>0</v>
       </c>
       <c r="J587" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K587" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>717</v>
       </c>
@@ -21433,7 +21442,7 @@
         <v>0</v>
       </c>
       <c r="E588" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F588">
@@ -21449,14 +21458,14 @@
         <v>0</v>
       </c>
       <c r="J588" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K588" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" s="3" t="s">
         <v>718</v>
       </c>
@@ -21470,7 +21479,7 @@
         <v>0</v>
       </c>
       <c r="E589" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F589">
@@ -21486,14 +21495,14 @@
         <v>0</v>
       </c>
       <c r="J589" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K589" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" s="3" t="s">
         <v>719</v>
       </c>
@@ -21507,7 +21516,7 @@
         <v>0</v>
       </c>
       <c r="E590" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F590">
@@ -21523,14 +21532,14 @@
         <v>0</v>
       </c>
       <c r="J590" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K590" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" s="3" t="s">
         <v>720</v>
       </c>
@@ -21544,7 +21553,7 @@
         <v>0</v>
       </c>
       <c r="E591" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F591">
@@ -21560,14 +21569,14 @@
         <v>0</v>
       </c>
       <c r="J591" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K591" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>721</v>
       </c>
@@ -21581,7 +21590,7 @@
         <v>0</v>
       </c>
       <c r="E592" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F592">
@@ -21597,14 +21606,14 @@
         <v>0</v>
       </c>
       <c r="J592" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K592" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" s="3" t="s">
         <v>722</v>
       </c>
@@ -21618,7 +21627,7 @@
         <v>0</v>
       </c>
       <c r="E593" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F593">
@@ -21634,14 +21643,14 @@
         <v>0</v>
       </c>
       <c r="J593" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K593" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" s="3" t="s">
         <v>723</v>
       </c>
@@ -21655,7 +21664,7 @@
         <v>0</v>
       </c>
       <c r="E594" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F594">
@@ -21671,14 +21680,14 @@
         <v>0</v>
       </c>
       <c r="J594" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K594" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" s="3" t="s">
         <v>724</v>
       </c>
@@ -21692,7 +21701,7 @@
         <v>0</v>
       </c>
       <c r="E595" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F595">
@@ -21708,14 +21717,14 @@
         <v>0</v>
       </c>
       <c r="J595" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K595" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" s="3" t="s">
         <v>725</v>
       </c>
@@ -21729,7 +21738,7 @@
         <v>0</v>
       </c>
       <c r="E596" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F596">
@@ -21745,14 +21754,14 @@
         <v>0</v>
       </c>
       <c r="J596" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K596" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" s="3" t="s">
         <v>726</v>
       </c>
@@ -21766,7 +21775,7 @@
         <v>0</v>
       </c>
       <c r="E597" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F597">
@@ -21782,7 +21791,7 @@
         <v>0</v>
       </c>
       <c r="J597" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K597" s="1" t="s">
@@ -21792,14 +21801,14 @@
     <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598"/>
       <c r="E598" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K598" s="1" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" s="3" t="s">
         <v>729</v>
       </c>
@@ -21813,7 +21822,7 @@
         <v>0</v>
       </c>
       <c r="E599" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F599">
@@ -21829,14 +21838,14 @@
         <v>0</v>
       </c>
       <c r="J599" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K599" s="1" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" s="3" t="s">
         <v>730</v>
       </c>
@@ -21850,7 +21859,7 @@
         <v>0</v>
       </c>
       <c r="E600" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F600">
@@ -21866,14 +21875,14 @@
         <v>0</v>
       </c>
       <c r="J600" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K600" s="1" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" s="3" t="s">
         <v>731</v>
       </c>
@@ -21887,7 +21896,7 @@
         <v>0</v>
       </c>
       <c r="E601" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F601" s="1">
@@ -21903,7 +21912,7 @@
         <v>0</v>
       </c>
       <c r="J601" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>FALSE</v>
       </c>
       <c r="K601" s="1" t="s">
@@ -21913,7 +21922,7 @@
     <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602"/>
       <c r="E602" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K602" s="1" t="s">
@@ -21923,7 +21932,7 @@
     <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603"/>
       <c r="E603" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K603" s="1" t="s">
@@ -21933,7 +21942,7 @@
     <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604"/>
       <c r="E604" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K604" s="1" t="s">
@@ -21943,14 +21952,14 @@
     <row r="605" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605"/>
       <c r="E605" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K605" s="1" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" s="3" t="s">
         <v>737</v>
       </c>
@@ -21964,7 +21973,7 @@
         <v>0</v>
       </c>
       <c r="E606" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F606">
@@ -21980,7 +21989,7 @@
         <v>2</v>
       </c>
       <c r="J606" t="str">
-        <f t="shared" ref="J606" si="41">IF(AND(AND((F606&gt;4), (F606&lt;=I606)),AND((G606&gt;3), (H606&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J606" si="43">IF(AND(AND((F606&gt;4), (F606&lt;=I606)),AND((G606&gt;3), (H606&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K606" s="1" t="s">
@@ -21990,7 +21999,7 @@
     <row r="607" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607"/>
       <c r="E607" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K607" s="1" t="s">
@@ -22000,7 +22009,7 @@
     <row r="608" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608"/>
       <c r="E608" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K608" s="1" t="s">
@@ -22010,14 +22019,14 @@
     <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609"/>
       <c r="E609" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K609" s="1" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" s="3" t="s">
         <v>793</v>
       </c>
@@ -22031,7 +22040,7 @@
         <v>0</v>
       </c>
       <c r="E610" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F610">
@@ -22047,7 +22056,7 @@
         <v>0</v>
       </c>
       <c r="J610" t="str">
-        <f t="shared" ref="J610" si="42">IF(AND(AND((F610&gt;4), (F610&lt;=I610)),AND((G610&gt;3), (H610&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J610" si="44">IF(AND(AND((F610&gt;4), (F610&lt;=I610)),AND((G610&gt;3), (H610&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K610" s="1" t="s">
@@ -22057,7 +22066,7 @@
     <row r="611" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611"/>
       <c r="E611" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K611" s="1" t="s">
@@ -22067,7 +22076,7 @@
     <row r="612" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612"/>
       <c r="E612" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K612" s="1" t="s">
@@ -22077,7 +22086,7 @@
     <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613"/>
       <c r="E613" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K613" s="1" t="s">
@@ -22087,7 +22096,7 @@
     <row r="614" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614"/>
       <c r="E614" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K614" s="1" t="s">
@@ -22097,14 +22106,14 @@
     <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615"/>
       <c r="E615" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K615" s="1" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" s="3" t="s">
         <v>794</v>
       </c>
@@ -22118,7 +22127,7 @@
         <v>0</v>
       </c>
       <c r="E616" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F616">
@@ -22134,14 +22143,14 @@
         <v>1</v>
       </c>
       <c r="J616" t="str">
-        <f t="shared" ref="J616:J619" si="43">IF(AND(AND((F616&gt;4), (F616&lt;=I616)),AND((G616&gt;3), (H616&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J616:J619" si="45">IF(AND(AND((F616&gt;4), (F616&lt;=I616)),AND((G616&gt;3), (H616&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K616" s="1" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" s="3" t="s">
         <v>795</v>
       </c>
@@ -22155,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="E617" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F617">
@@ -22171,7 +22180,7 @@
         <v>0</v>
       </c>
       <c r="J617" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>FALSE</v>
       </c>
       <c r="K617" s="1" t="s">
@@ -22181,14 +22190,14 @@
     <row r="618" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618"/>
       <c r="E618" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K618" s="1" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" s="3" t="s">
         <v>796</v>
       </c>
@@ -22202,7 +22211,7 @@
         <v>0</v>
       </c>
       <c r="E619" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F619">
@@ -22218,7 +22227,7 @@
         <v>0</v>
       </c>
       <c r="J619" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>FALSE</v>
       </c>
       <c r="K619" s="1" t="s">
@@ -22228,7 +22237,7 @@
     <row r="620" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620"/>
       <c r="E620" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K620" s="1" t="s">
@@ -22238,7 +22247,7 @@
     <row r="621" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621"/>
       <c r="E621" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K621" s="1" t="s">
@@ -22248,7 +22257,7 @@
     <row r="622" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622"/>
       <c r="E622" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K622" s="1" t="s">
@@ -22258,7 +22267,7 @@
     <row r="623" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623"/>
       <c r="E623" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K623" s="1" t="s">
@@ -22268,7 +22277,7 @@
     <row r="624" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624"/>
       <c r="E624" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K624" s="1" t="s">
@@ -22278,7 +22287,7 @@
     <row r="625" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625"/>
       <c r="E625" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K625" s="1" t="s">
@@ -22288,14 +22297,14 @@
     <row r="626" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626"/>
       <c r="E626" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K626" s="1" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" s="3" t="s">
         <v>789</v>
       </c>
@@ -22309,7 +22318,7 @@
         <v>0</v>
       </c>
       <c r="E627" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F627">
@@ -22325,14 +22334,14 @@
         <v>0</v>
       </c>
       <c r="J627" t="str">
-        <f t="shared" ref="J627:J630" si="44">IF(AND(AND((F627&gt;4), (F627&lt;=I627)),AND((G627&gt;3), (H627&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J627:J630" si="46">IF(AND(AND((F627&gt;4), (F627&lt;=I627)),AND((G627&gt;3), (H627&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K627" s="1" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" s="3" t="s">
         <v>790</v>
       </c>
@@ -22346,7 +22355,7 @@
         <v>0</v>
       </c>
       <c r="E628" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F628">
@@ -22362,14 +22371,14 @@
         <v>0</v>
       </c>
       <c r="J628" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>FALSE</v>
       </c>
       <c r="K628" s="1" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" s="3" t="s">
         <v>791</v>
       </c>
@@ -22383,7 +22392,7 @@
         <v>0</v>
       </c>
       <c r="E629" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F629">
@@ -22399,14 +22408,14 @@
         <v>0</v>
       </c>
       <c r="J629" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>FALSE</v>
       </c>
       <c r="K629" s="1" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" s="3" t="s">
         <v>792</v>
       </c>
@@ -22420,7 +22429,7 @@
         <v>0</v>
       </c>
       <c r="E630" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F630">
@@ -22436,7 +22445,7 @@
         <v>0</v>
       </c>
       <c r="J630" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>FALSE</v>
       </c>
       <c r="K630" s="1" t="s">
@@ -22446,7 +22455,7 @@
     <row r="631" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631"/>
       <c r="E631" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K631" s="1" t="s">
@@ -22456,7 +22465,7 @@
     <row r="632" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632"/>
       <c r="E632" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K632" s="1" t="s">
@@ -22466,7 +22475,7 @@
     <row r="633" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633"/>
       <c r="E633" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K633" s="1" t="s">
@@ -22476,14 +22485,14 @@
     <row r="634" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634"/>
       <c r="E634" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K634" s="1" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" s="3" t="s">
         <v>763</v>
       </c>
@@ -22497,7 +22506,7 @@
         <v>0</v>
       </c>
       <c r="E635" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F635">
@@ -22513,14 +22522,14 @@
         <v>1</v>
       </c>
       <c r="J635" t="str">
-        <f t="shared" ref="J635:J638" si="45">IF(AND(AND((F635&gt;4), (F635&lt;=I635)),AND((G635&gt;3), (H635&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J635:J638" si="47">IF(AND(AND((F635&gt;4), (F635&lt;=I635)),AND((G635&gt;3), (H635&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K635" s="1" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" s="3" t="s">
         <v>851</v>
       </c>
@@ -22534,7 +22543,7 @@
         <v>0</v>
       </c>
       <c r="E636" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F636">
@@ -22550,14 +22559,14 @@
         <v>0</v>
       </c>
       <c r="J636" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>FALSE</v>
       </c>
       <c r="K636" s="1" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" s="3" t="s">
         <v>797</v>
       </c>
@@ -22571,7 +22580,7 @@
         <v>0</v>
       </c>
       <c r="E637" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F637">
@@ -22587,14 +22596,14 @@
         <v>0</v>
       </c>
       <c r="J637" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>FALSE</v>
       </c>
       <c r="K637" s="1" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" s="3" t="s">
         <v>798</v>
       </c>
@@ -22608,7 +22617,7 @@
         <v>0</v>
       </c>
       <c r="E638" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>Yes</v>
       </c>
       <c r="F638">
@@ -22624,7 +22633,7 @@
         <v>1</v>
       </c>
       <c r="J638" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>FALSE</v>
       </c>
       <c r="K638" s="1" t="s">
@@ -22634,7 +22643,7 @@
     <row r="639" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639"/>
       <c r="E639" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K639" s="1" t="s">
@@ -22644,7 +22653,7 @@
     <row r="640" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640"/>
       <c r="E640" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K640" s="1" t="s">
@@ -22654,7 +22663,7 @@
     <row r="641" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641"/>
       <c r="E641" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>No</v>
       </c>
       <c r="K641" s="1" t="s">
@@ -22664,14 +22673,14 @@
     <row r="642" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642"/>
       <c r="E642" t="str">
-        <f t="shared" ref="E642:E692" si="46">IF(ISBLANK(A642), "No", "Yes")</f>
+        <f t="shared" ref="E642:E692" si="48">IF(ISBLANK(A642), "No", "Yes")</f>
         <v>No</v>
       </c>
       <c r="K642" s="1" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" s="3" t="s">
         <v>771</v>
       </c>
@@ -22685,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="E643" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F643">
@@ -22701,7 +22710,7 @@
         <v>1</v>
       </c>
       <c r="J643" t="str">
-        <f t="shared" ref="J643" si="47">IF(AND(AND((F643&gt;4), (F643&lt;=I643)),AND((G643&gt;3), (H643&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J643" si="49">IF(AND(AND((F643&gt;4), (F643&lt;=I643)),AND((G643&gt;3), (H643&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K643" s="1" t="s">
@@ -22711,7 +22720,7 @@
     <row r="644" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644"/>
       <c r="E644" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K644" s="1" t="s">
@@ -22721,7 +22730,7 @@
     <row r="645" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645"/>
       <c r="E645" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K645" s="1" t="s">
@@ -22731,7 +22740,7 @@
     <row r="646" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646"/>
       <c r="E646" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K646" s="1" t="s">
@@ -22741,7 +22750,7 @@
     <row r="647" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647"/>
       <c r="E647" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K647" s="1" t="s">
@@ -22751,7 +22760,7 @@
     <row r="648" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648"/>
       <c r="E648" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K648" s="1" t="s">
@@ -22761,7 +22770,7 @@
     <row r="649" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649"/>
       <c r="E649" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K649" s="1" t="s">
@@ -22771,7 +22780,7 @@
     <row r="650" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650"/>
       <c r="E650" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K650" s="1" t="s">
@@ -22781,14 +22790,14 @@
     <row r="651" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651"/>
       <c r="E651" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K651" s="1" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" s="3" t="s">
         <v>799</v>
       </c>
@@ -22802,7 +22811,7 @@
         <v>0</v>
       </c>
       <c r="E652" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F652">
@@ -22818,7 +22827,7 @@
         <v>0</v>
       </c>
       <c r="J652" t="str">
-        <f t="shared" ref="J652" si="48">IF(AND(AND((F652&gt;4), (F652&lt;=I652)),AND((G652&gt;3), (H652&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J652" si="50">IF(AND(AND((F652&gt;4), (F652&lt;=I652)),AND((G652&gt;3), (H652&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K652" s="1" t="s">
@@ -22828,14 +22837,14 @@
     <row r="653" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653"/>
       <c r="E653" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K653" s="1" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" s="3" t="s">
         <v>800</v>
       </c>
@@ -22849,7 +22858,7 @@
         <v>0</v>
       </c>
       <c r="E654" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F654">
@@ -22865,7 +22874,7 @@
         <v>0</v>
       </c>
       <c r="J654" t="str">
-        <f t="shared" ref="J654" si="49">IF(AND(AND((F654&gt;4), (F654&lt;=I654)),AND((G654&gt;3), (H654&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J654" si="51">IF(AND(AND((F654&gt;4), (F654&lt;=I654)),AND((G654&gt;3), (H654&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K654" s="1" t="s">
@@ -22875,7 +22884,7 @@
     <row r="655" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655"/>
       <c r="E655" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K655" s="1" t="s">
@@ -22885,14 +22894,14 @@
     <row r="656" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656"/>
       <c r="E656" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K656" s="1" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" s="3" t="s">
         <v>801</v>
       </c>
@@ -22906,7 +22915,7 @@
         <v>0</v>
       </c>
       <c r="E657" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F657">
@@ -22922,14 +22931,14 @@
         <v>0</v>
       </c>
       <c r="J657" t="str">
-        <f t="shared" ref="J657:J660" si="50">IF(AND(AND((F657&gt;4), (F657&lt;=I657)),AND((G657&gt;3), (H657&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J657:J660" si="52">IF(AND(AND((F657&gt;4), (F657&lt;=I657)),AND((G657&gt;3), (H657&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K657" s="1" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="658" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658" s="3" t="s">
         <v>802</v>
       </c>
@@ -22943,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="E658" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F658">
@@ -22959,14 +22968,14 @@
         <v>0</v>
       </c>
       <c r="J658" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>FALSE</v>
       </c>
       <c r="K658" s="1" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" s="3" t="s">
         <v>803</v>
       </c>
@@ -22980,7 +22989,7 @@
         <v>0</v>
       </c>
       <c r="E659" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F659">
@@ -22996,14 +23005,14 @@
         <v>0</v>
       </c>
       <c r="J659" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>FALSE</v>
       </c>
       <c r="K659" s="1" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" s="3" t="s">
         <v>804</v>
       </c>
@@ -23017,7 +23026,7 @@
         <v>0</v>
       </c>
       <c r="E660" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F660">
@@ -23033,7 +23042,7 @@
         <v>0</v>
       </c>
       <c r="J660" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>FALSE</v>
       </c>
       <c r="K660" s="1" t="s">
@@ -23043,7 +23052,7 @@
     <row r="661" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661"/>
       <c r="E661" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K661" s="1" t="s">
@@ -23053,14 +23062,14 @@
     <row r="662" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662"/>
       <c r="E662" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K662" s="1" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" s="3" t="s">
         <v>805</v>
       </c>
@@ -23074,7 +23083,7 @@
         <v>0</v>
       </c>
       <c r="E663" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F663">
@@ -23090,14 +23099,14 @@
         <v>0</v>
       </c>
       <c r="J663" t="str">
-        <f t="shared" ref="J663:J666" si="51">IF(AND(AND((F663&gt;4), (F663&lt;=I663)),AND((G663&gt;3), (H663&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J663:J666" si="53">IF(AND(AND((F663&gt;4), (F663&lt;=I663)),AND((G663&gt;3), (H663&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K663" s="1" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" s="3" t="s">
         <v>807</v>
       </c>
@@ -23111,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="E664" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F664">
@@ -23127,14 +23136,14 @@
         <v>0</v>
       </c>
       <c r="J664" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>FALSE</v>
       </c>
       <c r="K664" s="1" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" s="3" t="s">
         <v>806</v>
       </c>
@@ -23148,7 +23157,7 @@
         <v>0</v>
       </c>
       <c r="E665" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F665">
@@ -23164,14 +23173,14 @@
         <v>0</v>
       </c>
       <c r="J665" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>FALSE</v>
       </c>
       <c r="K665" s="1" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" s="3" t="s">
         <v>809</v>
       </c>
@@ -23185,7 +23194,7 @@
         <v>0</v>
       </c>
       <c r="E666" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F666">
@@ -23201,7 +23210,7 @@
         <v>1</v>
       </c>
       <c r="J666" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>FALSE</v>
       </c>
       <c r="K666" s="1" t="s">
@@ -23211,7 +23220,7 @@
     <row r="667" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667"/>
       <c r="E667" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K667" s="1" t="s">
@@ -23221,7 +23230,7 @@
     <row r="668" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668"/>
       <c r="E668" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K668" s="1" t="s">
@@ -23231,14 +23240,14 @@
     <row r="669" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669"/>
       <c r="E669" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K669" s="1" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" s="3" t="s">
         <v>814</v>
       </c>
@@ -23252,7 +23261,7 @@
         <v>0</v>
       </c>
       <c r="E670" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F670">
@@ -23268,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="J670" t="str">
-        <f t="shared" ref="J670" si="52">IF(AND(AND((F670&gt;4), (F670&lt;=I670)),AND((G670&gt;3), (H670&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J670" si="54">IF(AND(AND((F670&gt;4), (F670&lt;=I670)),AND((G670&gt;3), (H670&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K670" s="1" t="s">
@@ -23278,7 +23287,7 @@
     <row r="671" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671"/>
       <c r="E671" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K671" s="1" t="s">
@@ -23288,7 +23297,7 @@
     <row r="672" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672"/>
       <c r="E672" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K672" s="1" t="s">
@@ -23298,7 +23307,7 @@
     <row r="673" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673"/>
       <c r="E673" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K673" s="1" t="s">
@@ -23308,7 +23317,7 @@
     <row r="674" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674"/>
       <c r="E674" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K674" s="1" t="s">
@@ -23318,7 +23327,7 @@
     <row r="675" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675"/>
       <c r="E675" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K675" s="1" t="s">
@@ -23328,7 +23337,7 @@
     <row r="676" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676"/>
       <c r="E676" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K676" s="1" t="s">
@@ -23338,7 +23347,7 @@
     <row r="677" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677"/>
       <c r="E677" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K677" s="1" t="s">
@@ -23348,7 +23357,7 @@
     <row r="678" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678"/>
       <c r="E678" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K678" s="1" t="s">
@@ -23358,7 +23367,7 @@
     <row r="679" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679"/>
       <c r="E679" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K679" s="1" t="s">
@@ -23368,7 +23377,7 @@
     <row r="680" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680"/>
       <c r="E680" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K680" s="1" t="s">
@@ -23378,7 +23387,7 @@
     <row r="681" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681"/>
       <c r="E681" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K681" s="1" t="s">
@@ -23388,7 +23397,7 @@
     <row r="682" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682"/>
       <c r="E682" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K682" s="1" t="s">
@@ -23398,14 +23407,14 @@
     <row r="683" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683"/>
       <c r="E683" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K683" s="1" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" s="3" t="s">
         <v>830</v>
       </c>
@@ -23419,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="E684" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F684">
@@ -23435,7 +23444,7 @@
         <v>1</v>
       </c>
       <c r="J684" t="str">
-        <f t="shared" ref="J684" si="53">IF(AND(AND((F684&gt;4), (F684&lt;=I684)),AND((G684&gt;3), (H684&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J684" si="55">IF(AND(AND((F684&gt;4), (F684&lt;=I684)),AND((G684&gt;3), (H684&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K684" s="1" t="s">
@@ -23445,14 +23454,14 @@
     <row r="685" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685"/>
       <c r="E685" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K685" s="1" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686" s="3" t="s">
         <v>833</v>
       </c>
@@ -23466,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="E686" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F686">
@@ -23482,7 +23491,7 @@
         <v>1</v>
       </c>
       <c r="J686" t="str">
-        <f t="shared" ref="J686" si="54">IF(AND(AND((F686&gt;4), (F686&lt;=I686)),AND((G686&gt;3), (H686&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J686" si="56">IF(AND(AND((F686&gt;4), (F686&lt;=I686)),AND((G686&gt;3), (H686&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K686" s="1" t="s">
@@ -23492,7 +23501,7 @@
     <row r="687" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687"/>
       <c r="E687" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K687" s="1" t="s">
@@ -23502,7 +23511,7 @@
     <row r="688" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A688"/>
       <c r="E688" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K688" s="1" t="s">
@@ -23512,14 +23521,14 @@
     <row r="689" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689"/>
       <c r="E689" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K689" s="1" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="690" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" s="3" t="s">
         <v>838</v>
       </c>
@@ -23533,7 +23542,7 @@
         <v>0</v>
       </c>
       <c r="E690" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>Yes</v>
       </c>
       <c r="F690">
@@ -23549,7 +23558,7 @@
         <v>0</v>
       </c>
       <c r="J690" t="str">
-        <f t="shared" ref="J690" si="55">IF(AND(AND((F690&gt;4), (F690&lt;=I690)),AND((G690&gt;3), (H690&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J690" si="57">IF(AND(AND((F690&gt;4), (F690&lt;=I690)),AND((G690&gt;3), (H690&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K690" s="1" t="s">
@@ -23559,7 +23568,7 @@
     <row r="691" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691"/>
       <c r="E691" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K691" s="1" t="s">
@@ -23569,14 +23578,14 @@
     <row r="692" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692"/>
       <c r="E692" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>No</v>
       </c>
       <c r="K692" s="1" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="693" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693" s="3" t="s">
         <v>865</v>
       </c>
@@ -23605,14 +23614,14 @@
         <v>1</v>
       </c>
       <c r="J693" t="str">
-        <f t="shared" ref="J693:J712" si="56">IF(AND(AND((F693&gt;4), (F693&lt;=I693)),AND((G693&gt;3), (H693&lt;3))), "TRUE", "FALSE")</f>
+        <f t="shared" ref="J693:J712" si="58">IF(AND(AND((F693&gt;4), (F693&lt;=I693)),AND((G693&gt;3), (H693&lt;3))), "TRUE", "FALSE")</f>
         <v>FALSE</v>
       </c>
       <c r="K693" s="1" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="694" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694" s="3" t="s">
         <v>867</v>
       </c>
@@ -23641,14 +23650,14 @@
         <v>0</v>
       </c>
       <c r="J694" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K694" s="1" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="695" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695" s="3" t="s">
         <v>868</v>
       </c>
@@ -23677,14 +23686,14 @@
         <v>0</v>
       </c>
       <c r="J695" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K695" s="1" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="696" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696" s="3" t="s">
         <v>869</v>
       </c>
@@ -23713,14 +23722,14 @@
         <v>82</v>
       </c>
       <c r="J696" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K696" s="1" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="697" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697" s="3" t="s">
         <v>870</v>
       </c>
@@ -23749,14 +23758,14 @@
         <v>21</v>
       </c>
       <c r="J697" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K697" s="1" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="698" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698" s="3" t="s">
         <v>871</v>
       </c>
@@ -23785,14 +23794,14 @@
         <v>0</v>
       </c>
       <c r="J698" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K698" s="1" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="699" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699" s="3" t="s">
         <v>872</v>
       </c>
@@ -23821,14 +23830,14 @@
         <v>1</v>
       </c>
       <c r="J699" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K699" s="1" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="700" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" s="3" t="s">
         <v>873</v>
       </c>
@@ -23857,14 +23866,14 @@
         <v>1</v>
       </c>
       <c r="J700" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K700" s="1" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="701" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701" s="3" t="s">
         <v>874</v>
       </c>
@@ -23893,14 +23902,14 @@
         <v>1</v>
       </c>
       <c r="J701" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K701" s="1" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="702" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" s="3" t="s">
         <v>876</v>
       </c>
@@ -23929,7 +23938,7 @@
         <v>1</v>
       </c>
       <c r="J702" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K702" s="1" t="s">
@@ -23962,14 +23971,14 @@
         <v>11</v>
       </c>
       <c r="J703" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K703" s="1" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="704" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" s="3" t="s">
         <v>878</v>
       </c>
@@ -23998,14 +24007,14 @@
         <v>41</v>
       </c>
       <c r="J704" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K704" s="1" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="705" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" s="3" t="s">
         <v>881</v>
       </c>
@@ -24034,14 +24043,14 @@
         <v>7</v>
       </c>
       <c r="J705" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K705" s="1" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="706" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706" s="3" t="s">
         <v>882</v>
       </c>
@@ -24070,14 +24079,14 @@
         <v>17</v>
       </c>
       <c r="J706" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K706" s="1" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="707" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A707" s="3" t="s">
         <v>883</v>
       </c>
@@ -24106,14 +24115,14 @@
         <v>26</v>
       </c>
       <c r="J707" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K707" s="1" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="708" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708" s="3" t="s">
         <v>885</v>
       </c>
@@ -24142,14 +24151,14 @@
         <v>5</v>
       </c>
       <c r="J708" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K708" s="1" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="709" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" s="3" t="s">
         <v>887</v>
       </c>
@@ -24178,14 +24187,14 @@
         <v>11</v>
       </c>
       <c r="J709" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K709" s="1" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="710" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" s="3" t="s">
         <v>889</v>
       </c>
@@ -24214,14 +24223,14 @@
         <v>9</v>
       </c>
       <c r="J710" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K710" s="1" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="711" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" s="3" t="s">
         <v>890</v>
       </c>
@@ -24250,14 +24259,14 @@
         <v>35</v>
       </c>
       <c r="J711" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K711" s="1" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="712" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" s="3" t="s">
         <v>892</v>
       </c>
@@ -24286,7 +24295,7 @@
         <v>1</v>
       </c>
       <c r="J712" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>FALSE</v>
       </c>
       <c r="K712" s="1" t="s">
@@ -24304,6 +24313,11 @@
     <filterColumn colId="4">
       <filters>
         <filter val="Yes"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="TRUE"/>
       </filters>
     </filterColumn>
   </autoFilter>
